--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\137MHz-VHF-Satellite-LNA-Receiver\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7871854-64A0-4343-ADAA-49D44D6E60A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C022F80-BF70-475E-9AD7-F00A4F9DEAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="444" yWindow="396" windowWidth="22596" windowHeight="11844" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="81">
   <si>
     <t>Bill of Materials (BOM) — 137.5 MHz VHF Satellite LNA Receiver</t>
   </si>
@@ -270,13 +270,22 @@
   </si>
   <si>
     <t>Total component quantity:</t>
+  </si>
+  <si>
+    <t>SOT-223</t>
+  </si>
+  <si>
+    <t>TLV1117-50CDCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDO 5V fixed Output, Max Input Voltage 15V (U2) </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,6 +330,17 @@
       <color rgb="FF555555"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -376,18 +396,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -400,7 +411,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -675,615 +697,629 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="A4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
-        <v>1</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
-        <v>1</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="4">
+        <v>1</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
-        <v>1</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="4">
+        <v>1</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
-        <f>SUM(A6:A9)</f>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <f>SUM(A6:A10)</f>
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="11" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>2</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>1</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>2</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>1</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>1</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>1</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>1</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>2</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>1</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>1</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <f>SUM(A15:A25)</f>
+        <v>14</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-    </row>
-    <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+    </row>
+    <row r="29" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B30" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C30" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D30" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>1</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
+        <v>1</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
         <v>2</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
-        <v>1</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="B33" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
         <v>2</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
-        <v>1</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
-        <v>1</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="9">
-        <v>1</v>
-      </c>
-      <c r="B19" s="10" t="s">
+      <c r="B34" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>1</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>2</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>1</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>1</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>4</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>1</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>1</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="6">
+        <f>SUM(A31:A41)</f>
+        <v>17</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+    </row>
+    <row r="44" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
+        <v>1</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>1</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>1</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>2</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
+        <f>SUM(A46:A49)</f>
+        <v>5</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="1">
+        <f>COUNTA(B6:B10)+COUNTA(B15:B25)+COUNTA(B31:B41)+COUNTA(B46:B49)</f>
         <v>31</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>1</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="9">
-        <v>1</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
-        <v>2</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="9">
-        <v>1</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
-        <v>1</v>
-      </c>
-      <c r="B24" s="10" t="s">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="1">
+        <f>SUM(A6:A10)+SUM(A15:A25)+SUM(A31:A41)+SUM(A46:A49)</f>
         <v>42</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="11">
-        <f>SUM(A14:A24)</f>
-        <v>14</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-    </row>
-    <row r="26" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="28" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="9">
-        <v>1</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="9">
-        <v>1</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="9">
-        <v>2</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="9">
-        <v>2</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="9">
-        <v>1</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="9">
-        <v>2</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="9">
-        <v>1</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="9">
-        <v>1</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="9">
-        <v>2</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="9">
-        <v>1</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="9">
-        <v>1</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="11">
-        <f>SUM(A30:A40)</f>
-        <v>15</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-    </row>
-    <row r="43" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="9">
-        <v>1</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="9">
-        <v>1</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="9">
-        <v>1</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="9">
-        <v>2</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="11">
-        <f>SUM(A45:A48)</f>
-        <v>5</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="13">
-        <f>COUNTA(B6:B9)+COUNTA(B14:B24)+COUNTA(B30:B40)+COUNTA(B45:B48)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="13">
-        <f>SUM(A6:A9)+SUM(A14:A24)+SUM(A30:A40)+SUM(A45:A48)</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A55:D55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
